--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-01-2026.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>£23.87</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>£27.67</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£32.42</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£39.12</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£46.64</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>£19.98</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationuk.co.uk', port=443): Max retries exceeded with url: /products/75mm-celotex-ga4075-pir-insulation-board-2400mm-x-1200mm-x-75mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>£23.68</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>£25.87</t>
+          <t>£30.82</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>£26.35</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>£49.55</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>£73.80</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>£44.24</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£42.70</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
